--- a/artfynd/A 14768-2025 artfynd.xlsx
+++ b/artfynd/A 14768-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127765338</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58036</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14768-2025 artfynd.xlsx
+++ b/artfynd/A 14768-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127765338</v>
       </c>
       <c r="B2" t="n">
-        <v>58036</v>
+        <v>58042</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14768-2025 artfynd.xlsx
+++ b/artfynd/A 14768-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127765338</v>
       </c>
       <c r="B2" t="n">
-        <v>58042</v>
+        <v>58043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 14768-2025 artfynd.xlsx
+++ b/artfynd/A 14768-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>127765338</v>
       </c>
       <c r="B2" t="n">
-        <v>58043</v>
+        <v>58055</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
